--- a/받은 데이터/2월/비정기 목표(Irregular)_SD 외부채널.xlsx
+++ b/받은 데이터/2월/비정기 목표(Irregular)_SD 외부채널.xlsx
@@ -5,24 +5,27 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\효경\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Python\받은 데이터\2월\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00E362B1-E637-4D80-AC43-7223AAB4DDD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0079827B-D597-48E7-B5F5-69617FDC6C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1650" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="비정기목표" sheetId="1" r:id="rId1"/>
     <sheet name="안내" sheetId="2" r:id="rId2"/>
     <sheet name="목록" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">비정기목표!$A$1:$M$53</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2564" uniqueCount="2254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2582" uniqueCount="2254">
   <si>
     <t>ID</t>
   </si>
@@ -7196,7 +7199,9 @@
   <dimension ref="A1:M53"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="13" width="15.75" customWidth="1"/>
+    <col min="1" max="9" width="15.75" customWidth="1"/>
+    <col min="10" max="10" width="30.9140625" customWidth="1"/>
+    <col min="11" max="13" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
@@ -7266,16 +7271,16 @@
         <v>94</v>
       </c>
       <c r="J2" t="s">
-        <v>1915</v>
+        <v>1962</v>
       </c>
       <c r="K2">
-        <v>53300</v>
+        <v>3230000</v>
       </c>
       <c r="L2">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="M2" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
@@ -7304,16 +7309,16 @@
         <v>94</v>
       </c>
       <c r="J3" t="s">
-        <v>1962</v>
+        <v>1823</v>
       </c>
       <c r="K3">
-        <v>807500</v>
+        <v>821760</v>
       </c>
       <c r="L3">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="M3" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.45">
@@ -7342,16 +7347,16 @@
         <v>94</v>
       </c>
       <c r="J4" t="s">
-        <v>1829</v>
+        <v>1832</v>
       </c>
       <c r="K4">
-        <v>256800</v>
+        <v>847440</v>
       </c>
       <c r="L4">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="M4" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.45">
@@ -7380,16 +7385,16 @@
         <v>94</v>
       </c>
       <c r="J5" t="s">
-        <v>1823</v>
+        <v>1885</v>
       </c>
       <c r="K5">
-        <v>205440</v>
+        <v>1003200</v>
       </c>
       <c r="L5">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="M5" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.45">
@@ -7418,16 +7423,16 @@
         <v>94</v>
       </c>
       <c r="J6" t="s">
-        <v>1832</v>
+        <v>2248</v>
       </c>
       <c r="K6">
-        <v>211860</v>
+        <v>2052000</v>
       </c>
       <c r="L6">
-        <v>33</v>
+        <v>400</v>
       </c>
       <c r="M6" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.45">
@@ -7456,16 +7461,16 @@
         <v>94</v>
       </c>
       <c r="J7" t="s">
-        <v>1885</v>
+        <v>2249</v>
       </c>
       <c r="K7">
-        <v>250800</v>
+        <v>2093040</v>
       </c>
       <c r="L7">
-        <v>22</v>
+        <v>408</v>
       </c>
       <c r="M7" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.45">
@@ -7494,21 +7499,21 @@
         <v>94</v>
       </c>
       <c r="J8" t="s">
-        <v>1910</v>
+        <v>1877</v>
       </c>
       <c r="K8">
-        <v>558800</v>
+        <v>364800</v>
       </c>
       <c r="L8">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M8" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="B9" s="5" t="s">
-        <v>2246</v>
+      <c r="B9" t="s">
+        <v>2252</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
@@ -7520,7 +7525,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="6">
-        <v>46088</v>
+        <v>46112</v>
       </c>
       <c r="G9" s="7">
         <v>0.99998842592592596</v>
@@ -7532,21 +7537,21 @@
         <v>94</v>
       </c>
       <c r="J9" t="s">
-        <v>1807</v>
+        <v>1962</v>
       </c>
       <c r="K9">
-        <v>367200</v>
+        <v>4080000</v>
       </c>
       <c r="L9">
-        <v>15</v>
+        <v>240</v>
       </c>
       <c r="M9" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="B10" s="5" t="s">
-        <v>2246</v>
+      <c r="B10" t="s">
+        <v>2252</v>
       </c>
       <c r="C10" t="s">
         <v>32</v>
@@ -7558,7 +7563,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="6">
-        <v>46088</v>
+        <v>46112</v>
       </c>
       <c r="G10" s="7">
         <v>0.99998842592592596</v>
@@ -7570,21 +7575,21 @@
         <v>94</v>
       </c>
       <c r="J10" t="s">
-        <v>2072</v>
+        <v>1823</v>
       </c>
       <c r="K10">
-        <v>367200</v>
+        <v>828000</v>
       </c>
       <c r="L10">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="M10" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="B11" s="5" t="s">
-        <v>2246</v>
+      <c r="B11" t="s">
+        <v>2252</v>
       </c>
       <c r="C11" t="s">
         <v>32</v>
@@ -7596,7 +7601,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="6">
-        <v>46088</v>
+        <v>46112</v>
       </c>
       <c r="G11" s="7">
         <v>0.99998842592592596</v>
@@ -7608,21 +7613,21 @@
         <v>94</v>
       </c>
       <c r="J11" t="s">
-        <v>2248</v>
+        <v>1832</v>
       </c>
       <c r="K11">
-        <v>513000</v>
+        <v>828000</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="M11" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="B12" s="5" t="s">
-        <v>2246</v>
+      <c r="B12" t="s">
+        <v>2252</v>
       </c>
       <c r="C12" t="s">
         <v>32</v>
@@ -7634,7 +7639,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="6">
-        <v>46088</v>
+        <v>46112</v>
       </c>
       <c r="G12" s="7">
         <v>0.99998842592592596</v>
@@ -7646,21 +7651,21 @@
         <v>94</v>
       </c>
       <c r="J12" t="s">
-        <v>2249</v>
+        <v>1885</v>
       </c>
       <c r="K12">
-        <v>523260</v>
+        <v>1440000</v>
       </c>
       <c r="L12">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="M12" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="B13" s="5" t="s">
-        <v>2246</v>
+      <c r="B13" t="s">
+        <v>2252</v>
       </c>
       <c r="C13" t="s">
         <v>32</v>
@@ -7672,7 +7677,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="6">
-        <v>46088</v>
+        <v>46112</v>
       </c>
       <c r="G13" s="7">
         <v>0.99998842592592596</v>
@@ -7684,21 +7689,21 @@
         <v>94</v>
       </c>
       <c r="J13" t="s">
-        <v>1877</v>
+        <v>2248</v>
       </c>
       <c r="K13">
-        <v>91200</v>
+        <v>2376000</v>
       </c>
       <c r="L13">
-        <v>8</v>
+        <v>440</v>
       </c>
       <c r="M13" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="B14" s="5" t="s">
-        <v>2246</v>
+      <c r="B14" t="s">
+        <v>2252</v>
       </c>
       <c r="C14" t="s">
         <v>32</v>
@@ -7710,7 +7715,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="6">
-        <v>46088</v>
+        <v>46112</v>
       </c>
       <c r="G14" s="7">
         <v>0.99998842592592596</v>
@@ -7722,21 +7727,21 @@
         <v>94</v>
       </c>
       <c r="J14" t="s">
-        <v>1949</v>
+        <v>2249</v>
       </c>
       <c r="K14">
-        <v>1151400</v>
+        <v>2721600</v>
       </c>
       <c r="L14">
-        <v>60</v>
+        <v>504</v>
       </c>
       <c r="M14" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="B15" s="5" t="s">
-        <v>2246</v>
+      <c r="B15" t="s">
+        <v>2252</v>
       </c>
       <c r="C15" t="s">
         <v>32</v>
@@ -7748,7 +7753,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="6">
-        <v>46088</v>
+        <v>46112</v>
       </c>
       <c r="G15" s="7">
         <v>0.99998842592592596</v>
@@ -7760,33 +7765,33 @@
         <v>94</v>
       </c>
       <c r="J15" t="s">
-        <v>1869</v>
+        <v>1877</v>
       </c>
       <c r="K15">
-        <v>961250</v>
+        <v>528000</v>
       </c>
       <c r="L15">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="M15" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="B16" s="5" t="s">
-        <v>2246</v>
+      <c r="B16" t="s">
+        <v>2253</v>
       </c>
       <c r="C16" t="s">
         <v>32</v>
       </c>
       <c r="D16" s="6">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="E16" s="7">
         <v>0</v>
       </c>
       <c r="F16" s="6">
-        <v>46088</v>
+        <v>46142</v>
       </c>
       <c r="G16" s="7">
         <v>0.99998842592592596</v>
@@ -7798,33 +7803,33 @@
         <v>94</v>
       </c>
       <c r="J16" t="s">
-        <v>1962</v>
+        <v>2248</v>
       </c>
       <c r="K16">
-        <v>3230000</v>
+        <v>4320000</v>
       </c>
       <c r="L16">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="M16" t="s">
         <v>2251</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B17" s="5" t="s">
-        <v>2246</v>
+      <c r="B17" t="s">
+        <v>2253</v>
       </c>
       <c r="C17" t="s">
         <v>32</v>
       </c>
       <c r="D17" s="6">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="E17" s="7">
         <v>0</v>
       </c>
       <c r="F17" s="6">
-        <v>46088</v>
+        <v>46142</v>
       </c>
       <c r="G17" s="7">
         <v>0.99998842592592596</v>
@@ -7836,33 +7841,33 @@
         <v>94</v>
       </c>
       <c r="J17" t="s">
-        <v>1823</v>
+        <v>2249</v>
       </c>
       <c r="K17">
-        <v>821760</v>
+        <v>5184000</v>
       </c>
       <c r="L17">
-        <v>128</v>
+        <v>960</v>
       </c>
       <c r="M17" t="s">
         <v>2251</v>
       </c>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B18" s="5" t="s">
-        <v>2246</v>
+      <c r="B18" t="s">
+        <v>2253</v>
       </c>
       <c r="C18" t="s">
         <v>32</v>
       </c>
       <c r="D18" s="6">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="E18" s="7">
         <v>0</v>
       </c>
       <c r="F18" s="6">
-        <v>46088</v>
+        <v>46142</v>
       </c>
       <c r="G18" s="7">
         <v>0.99998842592592596</v>
@@ -7874,13 +7879,13 @@
         <v>94</v>
       </c>
       <c r="J18" t="s">
-        <v>1832</v>
+        <v>1877</v>
       </c>
       <c r="K18">
-        <v>847440</v>
+        <v>816000</v>
       </c>
       <c r="L18">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="M18" t="s">
         <v>2251</v>
@@ -7912,16 +7917,16 @@
         <v>94</v>
       </c>
       <c r="J19" t="s">
-        <v>1885</v>
+        <v>1915</v>
       </c>
       <c r="K19">
-        <v>1003200</v>
+        <v>53300</v>
       </c>
       <c r="L19">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="M19" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.45">
@@ -7950,16 +7955,16 @@
         <v>94</v>
       </c>
       <c r="J20" t="s">
-        <v>2248</v>
+        <v>1962</v>
       </c>
       <c r="K20">
-        <v>2052000</v>
+        <v>807500</v>
       </c>
       <c r="L20">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="M20" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.45">
@@ -7988,16 +7993,16 @@
         <v>94</v>
       </c>
       <c r="J21" t="s">
-        <v>2249</v>
+        <v>1829</v>
       </c>
       <c r="K21">
-        <v>2093040</v>
+        <v>256800</v>
       </c>
       <c r="L21">
-        <v>408</v>
+        <v>20</v>
       </c>
       <c r="M21" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.45">
@@ -8026,21 +8031,21 @@
         <v>94</v>
       </c>
       <c r="J22" t="s">
-        <v>1877</v>
+        <v>1823</v>
       </c>
       <c r="K22">
-        <v>364800</v>
+        <v>205440</v>
       </c>
       <c r="L22">
         <v>32</v>
       </c>
       <c r="M22" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B23" t="s">
-        <v>2252</v>
+      <c r="B23" s="5" t="s">
+        <v>2246</v>
       </c>
       <c r="C23" t="s">
         <v>32</v>
@@ -8052,7 +8057,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="6">
-        <v>46112</v>
+        <v>46088</v>
       </c>
       <c r="G23" s="7">
         <v>0.99998842592592596</v>
@@ -8064,21 +8069,21 @@
         <v>94</v>
       </c>
       <c r="J23" t="s">
-        <v>1915</v>
+        <v>1832</v>
       </c>
       <c r="K23">
-        <v>347400</v>
+        <v>211860</v>
       </c>
       <c r="L23">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="M23" t="s">
         <v>2250</v>
       </c>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B24" t="s">
-        <v>2252</v>
+      <c r="B24" s="5" t="s">
+        <v>2246</v>
       </c>
       <c r="C24" t="s">
         <v>32</v>
@@ -8090,7 +8095,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="6">
-        <v>46112</v>
+        <v>46088</v>
       </c>
       <c r="G24" s="7">
         <v>0.99998842592592596</v>
@@ -8102,21 +8107,21 @@
         <v>94</v>
       </c>
       <c r="J24" t="s">
-        <v>1962</v>
+        <v>1885</v>
       </c>
       <c r="K24">
-        <v>1020000</v>
+        <v>250800</v>
       </c>
       <c r="L24">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="M24" t="s">
         <v>2250</v>
       </c>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B25" t="s">
-        <v>2252</v>
+      <c r="B25" s="5" t="s">
+        <v>2246</v>
       </c>
       <c r="C25" t="s">
         <v>32</v>
@@ -8128,7 +8133,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="6">
-        <v>46112</v>
+        <v>46088</v>
       </c>
       <c r="G25" s="7">
         <v>0.99998842592592596</v>
@@ -8140,21 +8145,21 @@
         <v>94</v>
       </c>
       <c r="J25" t="s">
-        <v>1829</v>
+        <v>1910</v>
       </c>
       <c r="K25">
-        <v>276000</v>
+        <v>558800</v>
       </c>
       <c r="L25">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="M25" t="s">
         <v>2250</v>
       </c>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B26" t="s">
-        <v>2252</v>
+      <c r="B26" s="5" t="s">
+        <v>2246</v>
       </c>
       <c r="C26" t="s">
         <v>32</v>
@@ -8166,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="6">
-        <v>46112</v>
+        <v>46088</v>
       </c>
       <c r="G26" s="7">
         <v>0.99998842592592596</v>
@@ -8178,21 +8183,21 @@
         <v>94</v>
       </c>
       <c r="J26" t="s">
-        <v>1823</v>
+        <v>1807</v>
       </c>
       <c r="K26">
-        <v>207000</v>
+        <v>367200</v>
       </c>
       <c r="L26">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="M26" t="s">
         <v>2250</v>
       </c>
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B27" t="s">
-        <v>2252</v>
+      <c r="B27" s="5" t="s">
+        <v>2246</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
@@ -8204,7 +8209,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="6">
-        <v>46112</v>
+        <v>46088</v>
       </c>
       <c r="G27" s="7">
         <v>0.99998842592592596</v>
@@ -8216,21 +8221,21 @@
         <v>94</v>
       </c>
       <c r="J27" t="s">
-        <v>1832</v>
+        <v>2072</v>
       </c>
       <c r="K27">
-        <v>207000</v>
+        <v>367200</v>
       </c>
       <c r="L27">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="M27" t="s">
         <v>2250</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B28" t="s">
-        <v>2252</v>
+      <c r="B28" s="5" t="s">
+        <v>2246</v>
       </c>
       <c r="C28" t="s">
         <v>32</v>
@@ -8242,7 +8247,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="6">
-        <v>46112</v>
+        <v>46088</v>
       </c>
       <c r="G28" s="7">
         <v>0.99998842592592596</v>
@@ -8254,21 +8259,21 @@
         <v>94</v>
       </c>
       <c r="J28" t="s">
-        <v>1885</v>
+        <v>2248</v>
       </c>
       <c r="K28">
-        <v>360000</v>
+        <v>513000</v>
       </c>
       <c r="L28">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="M28" t="s">
         <v>2250</v>
       </c>
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B29" t="s">
-        <v>2252</v>
+      <c r="B29" s="5" t="s">
+        <v>2246</v>
       </c>
       <c r="C29" t="s">
         <v>32</v>
@@ -8280,7 +8285,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="6">
-        <v>46112</v>
+        <v>46088</v>
       </c>
       <c r="G29" s="7">
         <v>0.99998842592592596</v>
@@ -8292,21 +8297,21 @@
         <v>94</v>
       </c>
       <c r="J29" t="s">
-        <v>1910</v>
+        <v>2249</v>
       </c>
       <c r="K29">
-        <v>576000</v>
+        <v>523260</v>
       </c>
       <c r="L29">
-        <v>40</v>
+        <v>102</v>
       </c>
       <c r="M29" t="s">
         <v>2250</v>
       </c>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B30" t="s">
-        <v>2252</v>
+      <c r="B30" s="5" t="s">
+        <v>2246</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
@@ -8318,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="6">
-        <v>46112</v>
+        <v>46088</v>
       </c>
       <c r="G30" s="7">
         <v>0.99998842592592596</v>
@@ -8330,21 +8335,21 @@
         <v>94</v>
       </c>
       <c r="J30" t="s">
-        <v>1807</v>
+        <v>1877</v>
       </c>
       <c r="K30">
-        <v>864000</v>
+        <v>91200</v>
       </c>
       <c r="L30">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="M30" t="s">
         <v>2250</v>
       </c>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B31" t="s">
-        <v>2252</v>
+      <c r="B31" s="5" t="s">
+        <v>2246</v>
       </c>
       <c r="C31" t="s">
         <v>32</v>
@@ -8356,7 +8361,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="6">
-        <v>46112</v>
+        <v>46088</v>
       </c>
       <c r="G31" s="7">
         <v>0.99998842592592596</v>
@@ -8368,21 +8373,21 @@
         <v>94</v>
       </c>
       <c r="J31" t="s">
-        <v>2072</v>
+        <v>1949</v>
       </c>
       <c r="K31">
-        <v>864000</v>
+        <v>1151400</v>
       </c>
       <c r="L31">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="M31" t="s">
         <v>2250</v>
       </c>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B32" t="s">
-        <v>2252</v>
+      <c r="B32" s="5" t="s">
+        <v>2246</v>
       </c>
       <c r="C32" t="s">
         <v>32</v>
@@ -8394,7 +8399,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="6">
-        <v>46112</v>
+        <v>46088</v>
       </c>
       <c r="G32" s="7">
         <v>0.99998842592592596</v>
@@ -8409,10 +8414,10 @@
         <v>1869</v>
       </c>
       <c r="K32">
-        <v>894000</v>
+        <v>961250</v>
       </c>
       <c r="L32">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M32" t="s">
         <v>2250</v>
@@ -8444,13 +8449,13 @@
         <v>94</v>
       </c>
       <c r="J33" t="s">
-        <v>2248</v>
+        <v>1915</v>
       </c>
       <c r="K33">
-        <v>594000</v>
+        <v>347400</v>
       </c>
       <c r="L33">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="M33" t="s">
         <v>2250</v>
@@ -8482,13 +8487,13 @@
         <v>94</v>
       </c>
       <c r="J34" t="s">
-        <v>2249</v>
+        <v>1962</v>
       </c>
       <c r="K34">
-        <v>680400</v>
+        <v>1020000</v>
       </c>
       <c r="L34">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="M34" t="s">
         <v>2250</v>
@@ -8520,13 +8525,13 @@
         <v>94</v>
       </c>
       <c r="J35" t="s">
-        <v>1877</v>
+        <v>1829</v>
       </c>
       <c r="K35">
-        <v>132000</v>
+        <v>276000</v>
       </c>
       <c r="L35">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="M35" t="s">
         <v>2250</v>
@@ -8558,13 +8563,13 @@
         <v>94</v>
       </c>
       <c r="J36" t="s">
-        <v>1949</v>
+        <v>1823</v>
       </c>
       <c r="K36">
-        <v>1110450</v>
+        <v>207000</v>
       </c>
       <c r="L36">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="M36" t="s">
         <v>2250</v>
@@ -8596,16 +8601,16 @@
         <v>94</v>
       </c>
       <c r="J37" t="s">
-        <v>1962</v>
+        <v>1832</v>
       </c>
       <c r="K37">
-        <v>4080000</v>
+        <v>207000</v>
       </c>
       <c r="L37">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="M37" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.45">
@@ -8634,16 +8639,16 @@
         <v>94</v>
       </c>
       <c r="J38" t="s">
-        <v>1823</v>
+        <v>1885</v>
       </c>
       <c r="K38">
-        <v>828000</v>
+        <v>360000</v>
       </c>
       <c r="L38">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="M38" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.45">
@@ -8672,16 +8677,16 @@
         <v>94</v>
       </c>
       <c r="J39" t="s">
-        <v>1832</v>
+        <v>1910</v>
       </c>
       <c r="K39">
-        <v>828000</v>
+        <v>576000</v>
       </c>
       <c r="L39">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="M39" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.45">
@@ -8710,16 +8715,16 @@
         <v>94</v>
       </c>
       <c r="J40" t="s">
-        <v>1885</v>
+        <v>1807</v>
       </c>
       <c r="K40">
-        <v>1440000</v>
+        <v>864000</v>
       </c>
       <c r="L40">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="M40" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.45">
@@ -8748,16 +8753,16 @@
         <v>94</v>
       </c>
       <c r="J41" t="s">
-        <v>2248</v>
+        <v>2072</v>
       </c>
       <c r="K41">
-        <v>2376000</v>
+        <v>864000</v>
       </c>
       <c r="L41">
-        <v>440</v>
+        <v>30</v>
       </c>
       <c r="M41" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.45">
@@ -8786,16 +8791,16 @@
         <v>94</v>
       </c>
       <c r="J42" t="s">
-        <v>2249</v>
+        <v>1869</v>
       </c>
       <c r="K42">
-        <v>2721600</v>
+        <v>894000</v>
       </c>
       <c r="L42">
-        <v>504</v>
+        <v>20</v>
       </c>
       <c r="M42" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.45">
@@ -8824,33 +8829,33 @@
         <v>94</v>
       </c>
       <c r="J43" t="s">
-        <v>1877</v>
+        <v>2248</v>
       </c>
       <c r="K43">
-        <v>528000</v>
+        <v>594000</v>
       </c>
       <c r="L43">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="M43" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="C44" t="s">
         <v>32</v>
       </c>
       <c r="D44" s="6">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="E44" s="7">
         <v>0</v>
       </c>
       <c r="F44" s="6">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="G44" s="7">
         <v>0.99998842592592596</v>
@@ -8862,27 +8867,33 @@
         <v>94</v>
       </c>
       <c r="J44" t="s">
-        <v>1807</v>
+        <v>2249</v>
       </c>
       <c r="K44">
-        <v>720000</v>
+        <v>680400</v>
       </c>
       <c r="L44">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="M44" t="s">
         <v>2250</v>
       </c>
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B45" t="s">
+        <v>2252</v>
+      </c>
+      <c r="C45" t="s">
+        <v>32</v>
+      </c>
       <c r="D45" s="6">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="E45" s="7">
         <v>0</v>
       </c>
       <c r="F45" s="6">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="G45" s="7">
         <v>0.99998842592592596</v>
@@ -8894,27 +8905,33 @@
         <v>94</v>
       </c>
       <c r="J45" t="s">
-        <v>2072</v>
+        <v>1877</v>
       </c>
       <c r="K45">
-        <v>576000</v>
+        <v>132000</v>
       </c>
       <c r="L45">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="M45" t="s">
         <v>2250</v>
       </c>
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B46" t="s">
+        <v>2252</v>
+      </c>
+      <c r="C46" t="s">
+        <v>32</v>
+      </c>
       <c r="D46" s="6">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="E46" s="7">
         <v>0</v>
       </c>
       <c r="F46" s="6">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="G46" s="7">
         <v>0.99998842592592596</v>
@@ -8926,19 +8943,25 @@
         <v>94</v>
       </c>
       <c r="J46" t="s">
-        <v>1869</v>
+        <v>1949</v>
       </c>
       <c r="K46">
-        <v>447000</v>
+        <v>1110450</v>
       </c>
       <c r="L46">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="M46" t="s">
         <v>2250</v>
       </c>
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B47" t="s">
+        <v>2253</v>
+      </c>
+      <c r="C47" t="s">
+        <v>32</v>
+      </c>
       <c r="D47" s="6">
         <v>46113</v>
       </c>
@@ -8958,19 +8981,25 @@
         <v>94</v>
       </c>
       <c r="J47" t="s">
-        <v>2248</v>
+        <v>1807</v>
       </c>
       <c r="K47">
-        <v>1080000</v>
+        <v>720000</v>
       </c>
       <c r="L47">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="M47" t="s">
         <v>2250</v>
       </c>
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B48" t="s">
+        <v>2253</v>
+      </c>
+      <c r="C48" t="s">
+        <v>32</v>
+      </c>
       <c r="D48" s="6">
         <v>46113</v>
       </c>
@@ -8990,19 +9019,25 @@
         <v>94</v>
       </c>
       <c r="J48" t="s">
-        <v>2249</v>
+        <v>2072</v>
       </c>
       <c r="K48">
-        <v>1296000</v>
+        <v>576000</v>
       </c>
       <c r="L48">
-        <v>240</v>
+        <v>20</v>
       </c>
       <c r="M48" t="s">
         <v>2250</v>
       </c>
     </row>
-    <row r="49" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B49" t="s">
+        <v>2253</v>
+      </c>
+      <c r="C49" t="s">
+        <v>32</v>
+      </c>
       <c r="D49" s="6">
         <v>46113</v>
       </c>
@@ -9022,19 +9057,25 @@
         <v>94</v>
       </c>
       <c r="J49" t="s">
-        <v>1877</v>
+        <v>1869</v>
       </c>
       <c r="K49">
-        <v>204000</v>
+        <v>447000</v>
       </c>
       <c r="L49">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="M49" t="s">
         <v>2250</v>
       </c>
     </row>
-    <row r="50" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B50" t="s">
+        <v>2253</v>
+      </c>
+      <c r="C50" t="s">
+        <v>32</v>
+      </c>
       <c r="D50" s="6">
         <v>46113</v>
       </c>
@@ -9054,19 +9095,25 @@
         <v>94</v>
       </c>
       <c r="J50" t="s">
-        <v>1949</v>
+        <v>2248</v>
       </c>
       <c r="K50">
-        <v>1413300</v>
+        <v>1080000</v>
       </c>
       <c r="L50">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="M50" t="s">
         <v>2250</v>
       </c>
     </row>
-    <row r="51" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B51" t="s">
+        <v>2253</v>
+      </c>
+      <c r="C51" t="s">
+        <v>32</v>
+      </c>
       <c r="D51" s="6">
         <v>46113</v>
       </c>
@@ -9086,19 +9133,25 @@
         <v>94</v>
       </c>
       <c r="J51" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="K51">
-        <v>4320000</v>
+        <v>1296000</v>
       </c>
       <c r="L51">
-        <v>800</v>
+        <v>240</v>
       </c>
       <c r="M51" t="s">
-        <v>2251</v>
-      </c>
-    </row>
-    <row r="52" spans="4:13" x14ac:dyDescent="0.45">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B52" t="s">
+        <v>2253</v>
+      </c>
+      <c r="C52" t="s">
+        <v>32</v>
+      </c>
       <c r="D52" s="6">
         <v>46113</v>
       </c>
@@ -9118,19 +9171,25 @@
         <v>94</v>
       </c>
       <c r="J52" t="s">
-        <v>2249</v>
+        <v>1877</v>
       </c>
       <c r="K52">
-        <v>5184000</v>
+        <v>204000</v>
       </c>
       <c r="L52">
-        <v>960</v>
+        <v>17</v>
       </c>
       <c r="M52" t="s">
-        <v>2251</v>
-      </c>
-    </row>
-    <row r="53" spans="4:13" x14ac:dyDescent="0.45">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="53" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B53" t="s">
+        <v>2253</v>
+      </c>
+      <c r="C53" t="s">
+        <v>32</v>
+      </c>
       <c r="D53" s="6">
         <v>46113</v>
       </c>
@@ -9150,19 +9209,20 @@
         <v>94</v>
       </c>
       <c r="J53" t="s">
-        <v>1877</v>
+        <v>1949</v>
       </c>
       <c r="K53">
-        <v>816000</v>
+        <v>1413300</v>
       </c>
       <c r="L53">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M53" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M53" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
